--- a/Documentation/Playback_Switch_BOM.xlsx
+++ b/Documentation/Playback_Switch_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bradw\GitHub\Playback-Switch\Documentation\Working_Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://neilsquiresoc-my.sharepoint.com/personal/bradw_neilsquire_ca/Documents/Documents/GitHub/Playback-Switch/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03334379-F0E2-47D1-954A-ADFE0106759E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C7EBAF6-E383-4911-9F92-89D5DC878B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -118,9 +118,6 @@
     <t>3.5mm audio cable</t>
   </si>
   <si>
-    <t>https://www.digikey.ca/en/products/detail/cnc-tech/770-10040-00050/3868284</t>
-  </si>
-  <si>
     <t>Cable Tie</t>
   </si>
   <si>
@@ -188,6 +185,9 @@
   </si>
   <si>
     <t>Recording button 8 pack</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/tensility-international-corp/10-00344/2350247</t>
   </si>
 </sst>
 </file>
@@ -806,22 +806,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="89.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="89.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="89.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="89.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="36" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:12" ht="35.25" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -835,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -844,7 +844,7 @@
       </c>
       <c r="C2" s="5">
         <f>SUM(G5:G12)+E19</f>
-        <v>7.2975000000000003</v>
+        <v>8.8825000000000003</v>
       </c>
       <c r="D2" s="24">
         <f>SUM(F14:F18)/60</f>
@@ -855,12 +855,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -889,7 +889,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -917,7 +917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -945,7 +945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -956,29 +956,29 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="9">
-        <v>4.01</v>
+        <v>3.59</v>
       </c>
       <c r="F7" s="17">
         <f t="shared" ref="F7:F8" si="0">E7/D7</f>
-        <v>2.0049999999999999</v>
+        <v>3.59</v>
       </c>
       <c r="G7" s="17">
         <f>F7*C7</f>
-        <v>2.0049999999999999</v>
+        <v>3.59</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -998,21 +998,21 @@
         <v>0.15</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F9" s="17"/>
       <c r="G9" s="18"/>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="27"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="28">
         <v>25</v>
@@ -1022,68 +1022,68 @@
       <c r="G12" s="23"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="26" t="s">
         <v>26</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>27</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E14" s="17">
         <f>(D14/1000)*$B$12</f>
         <v>0</v>
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E15" s="17">
         <f t="shared" ref="E15:E18" si="1">(D15/1000)*$B$12</f>
         <v>0</v>
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E16" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E17" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E18" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="D19" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="21">
         <f>SUM(E14:E18)</f>
@@ -1091,9 +1091,9 @@
       </c>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1107,39 +1107,39 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="29" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="29" t="s">
-        <v>39</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1153,36 +1153,36 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>44</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1447,6 +1447,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="38b325e6-602c-452a-8617-173bf47082c5" xsi:nil="true"/>
@@ -1455,15 +1464,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1486,6 +1486,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4740145F-09D2-466B-B9A2-2798696B0ADF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4958292-C6C4-482B-887A-6CF9FB19AB74}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1494,12 +1502,4 @@
     <ds:schemaRef ds:uri="8cf100d1-0775-4feb-8634-62999c4541bc"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4740145F-09D2-466B-B9A2-2798696B0ADF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>